--- a/data/dividends_info_20260315.xlsx
+++ b/data/dividends_info_20260315.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,11 +538,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5</v>
+        <v>0.376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -551,12 +551,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -566,30 +566,30 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>IT0004998065</t>
+          <t>IT0000214293</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6.614999771118164</v>
+        <v>17.79999923706055</v>
       </c>
       <c r="I3" t="n">
-        <v>7.558579248680498</v>
+        <v>2.112359641101265</v>
       </c>
       <c r="J3" t="n">
-        <v>36</v>
+        <v>127</v>
       </c>
       <c r="K3" t="n">
-        <v>38</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.54</v>
+        <v>0.25</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -598,45 +598,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Straordinario</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>IT0005218380</t>
+          <t>IT0001207098</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>11.43000030517578</v>
+        <v>24.18000030517578</v>
       </c>
       <c r="I4" t="n">
-        <v>4.724409322679326</v>
+        <v>1.033912311185898</v>
       </c>
       <c r="J4" t="n">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="K4" t="n">
-        <v>38</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1</v>
+        <v>0.195</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -645,12 +645,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -660,30 +660,30 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>NL0015435975</t>
+          <t>IT0005331019</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6.176000118255615</v>
+        <v>22.04999923706055</v>
       </c>
       <c r="I5" t="n">
-        <v>1.619170953452711</v>
+        <v>0.8843537720956184</v>
       </c>
       <c r="J5" t="n">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="K5" t="n">
-        <v>38</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.16</v>
+        <v>0.63</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -692,12 +692,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -707,30 +707,30 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>IT0005215329</t>
+          <t>IT0003856405</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>9.100000381469727</v>
+        <v>64.08000183105469</v>
       </c>
       <c r="I6" t="n">
-        <v>1.758241684536706</v>
+        <v>0.9831460393228127</v>
       </c>
       <c r="J6" t="n">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="K6" t="n">
-        <v>38</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.14</v>
+        <v>0.85</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -739,12 +739,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -754,30 +754,30 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>IT0001214433</t>
+          <t>IT0003796171</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>22.20000076293945</v>
+        <v>21.18000030517578</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6306306089579743</v>
+        <v>4.013219961060551</v>
       </c>
       <c r="J7" t="n">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="K7" t="n">
-        <v>31</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06</v>
+        <v>0.1813</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -801,30 +801,30 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>IT0005418204</t>
+          <t>IT0003153415</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.509999990463257</v>
+        <v>6.613999843597412</v>
       </c>
       <c r="I8" t="n">
-        <v>3.973509958870426</v>
+        <v>2.74115519031203</v>
       </c>
       <c r="J8" t="n">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="K8" t="n">
-        <v>31</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.034</v>
+        <v>0.29</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -833,12 +833,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -848,30 +848,30 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>IT0005379604</t>
+          <t>IT0004056880</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1.929999947547913</v>
+        <v>10.52000045776367</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7616580789651</v>
+        <v>2.756653872443346</v>
       </c>
       <c r="J9" t="n">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="K9" t="n">
-        <v>17</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.26</v>
+        <v>1.64</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -880,82 +880,2620 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>IT0003132476</t>
+          <t>IT0000062072</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>22.35000038146973</v>
+        <v>34.20999908447266</v>
       </c>
       <c r="I10" t="n">
-        <v>1.163310942113293</v>
+        <v>4.793920034754892</v>
       </c>
       <c r="J10" t="n">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="K10" t="n">
-        <v>10</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>AZIMUT HOLDING S.p.A.</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>IT0003261697</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>32.13999938964844</v>
+      </c>
+      <c r="I11" t="n">
+        <v>6.222775475982599</v>
+      </c>
+      <c r="J11" t="n">
+        <v>64</v>
+      </c>
+      <c r="K11" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ariston Holding N.V.</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NL0015000N33</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>3.865999937057495</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.58665291329809</v>
+      </c>
+      <c r="J12" t="n">
+        <v>64</v>
+      </c>
+      <c r="K12" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Avio S.p.A.</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.14846</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>IT0005119810</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.4067397260273973</v>
+      </c>
+      <c r="J13" t="n">
+        <v>64</v>
+      </c>
+      <c r="K13" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>IT0004764699</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>70.33999633789062</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.478532917465869</v>
+      </c>
+      <c r="J14" t="n">
+        <v>64</v>
+      </c>
+      <c r="K14" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Banca Generali S.p.A.</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Interim</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>IT0001031084</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>50.29999923706055</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.373757521608592</v>
+      </c>
+      <c r="J15" t="n">
+        <v>64</v>
+      </c>
+      <c r="K15" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>IT0005508921</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>7.13700008392334</v>
+      </c>
+      <c r="I16" t="n">
+        <v>12.04988076064646</v>
+      </c>
+      <c r="J16" t="n">
+        <v>64</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bper Banca S.P.A.</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>IT0000066123</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>10.97000026702881</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5.104831233989334</v>
+      </c>
+      <c r="J17" t="n">
+        <v>64</v>
+      </c>
+      <c r="K17" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>IT0001472171</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1.809999942779541</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.209944821245335</v>
+      </c>
+      <c r="J18" t="n">
+        <v>64</v>
+      </c>
+      <c r="K18" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Cementir Holding N.V.</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>NL0013995087</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>14.4399995803833</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.077562387242373</v>
+      </c>
+      <c r="J19" t="n">
+        <v>64</v>
+      </c>
+      <c r="K19" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ERG S.p.A.</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>IT0001157020</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>21.78000068664551</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.591368082982449</v>
+      </c>
+      <c r="J20" t="n">
+        <v>64</v>
+      </c>
+      <c r="K20" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Enervit S.p.A.</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>IT0004356751</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>4.099999904632568</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5.243902560999395</v>
+      </c>
+      <c r="J21" t="n">
+        <v>64</v>
+      </c>
+      <c r="K21" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>FinecoBank S.p.A.</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>IT0000072170</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>18.69499969482422</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.225728873473662</v>
+      </c>
+      <c r="J22" t="n">
+        <v>64</v>
+      </c>
+      <c r="K22" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Intesa Sanpaolo S.p.A.</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>IT0000072618</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>5.144000053405762</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3.693623600843549</v>
+      </c>
+      <c r="J23" t="n">
+        <v>64</v>
+      </c>
+      <c r="K23" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Italgas S.p.A.</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>IT0005211237</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>10.19999980926514</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4.235294196844927</v>
+      </c>
+      <c r="J24" t="n">
+        <v>64</v>
+      </c>
+      <c r="K24" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Lottomatica Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>IT0005541336</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>24.78000068664551</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.775625455237077</v>
+      </c>
+      <c r="J25" t="n">
+        <v>64</v>
+      </c>
+      <c r="K25" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Moncler S.p.A.</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>IT0004965148</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>52.56000137329102</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.663622457040928</v>
+      </c>
+      <c r="J26" t="n">
+        <v>64</v>
+      </c>
+      <c r="K26" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Nexi S.p.A.</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>IT0005366767</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>2.983000040054321</v>
+      </c>
+      <c r="I27" t="n">
+        <v>10.05698947273688</v>
+      </c>
+      <c r="J27" t="n">
+        <v>64</v>
+      </c>
+      <c r="K27" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>REPLY S.p.A.</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>IT0005282865</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>87.15000152587891</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.549053329160438</v>
+      </c>
+      <c r="J28" t="n">
+        <v>64</v>
+      </c>
+      <c r="K28" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SAIPEM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>IT0005495657</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>3.36899995803833</v>
+      </c>
+      <c r="I29" t="n">
+        <v>5.046007780272756</v>
+      </c>
+      <c r="J29" t="n">
+        <v>64</v>
+      </c>
+      <c r="K29" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SYS-DAT S.p.A.</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>IT0005595423</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>4.53000020980835</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.8830021666090007</v>
+      </c>
+      <c r="J30" t="n">
+        <v>64</v>
+      </c>
+      <c r="K30" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sanlorenzo S.p.A.</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>IT0003549422</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>29.39999961853027</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3.571428617768432</v>
+      </c>
+      <c r="J31" t="n">
+        <v>64</v>
+      </c>
+      <c r="K31" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TENARIS S.A.</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>DOLLARI USA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>LU2598331598</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>23.04000091552734</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.604166563186384</v>
+      </c>
+      <c r="J32" t="n">
+        <v>64</v>
+      </c>
+      <c r="K32" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>WEBUILD S.p.A.</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>IT0003865570</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>2.476000070571899</v>
+      </c>
+      <c r="I33" t="n">
+        <v>10.50080745514462</v>
+      </c>
+      <c r="J33" t="n">
+        <v>64</v>
+      </c>
+      <c r="K33" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ZIGNAGO VETRO S.p.A.</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>IT0004171440</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>6.809999942779541</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3.230543345793418</v>
+      </c>
+      <c r="J34" t="n">
+        <v>57</v>
+      </c>
+      <c r="K34" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ASCOPIAVE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>IT0004093263</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>3.569999933242798</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4.481792800894103</v>
+      </c>
+      <c r="J35" t="n">
+        <v>50</v>
+      </c>
+      <c r="K35" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Alerion Clean Power S.p.A.</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>IT0004720733</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>18.3799991607666</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3.318824961113642</v>
+      </c>
+      <c r="J36" t="n">
+        <v>50</v>
+      </c>
+      <c r="K36" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.5105</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>IT0001041000</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>8.510000228881836</v>
+      </c>
+      <c r="I37" t="n">
+        <v>5.998824750526201</v>
+      </c>
+      <c r="J37" t="n">
+        <v>50</v>
+      </c>
+      <c r="K37" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>DOLLARI USA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>LU2592315662</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>6.949999809265137</v>
+      </c>
+      <c r="I38" t="n">
+        <v>3.884892192947393</v>
+      </c>
+      <c r="J38" t="n">
+        <v>50</v>
+      </c>
+      <c r="K38" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Esprinet S.p.A.</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>IT0003850929</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>4.519999980926514</v>
+      </c>
+      <c r="I39" t="n">
+        <v>7.743362864533833</v>
+      </c>
+      <c r="J39" t="n">
+        <v>50</v>
+      </c>
+      <c r="K39" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>First Capital S.p.A.</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Straordinario</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>IT0005252736</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>18.79999923706055</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3.989361864023487</v>
+      </c>
+      <c r="J40" t="n">
+        <v>50</v>
+      </c>
+      <c r="K40" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>GEFRAN S.p.A.</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>IT0003203947</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>10.30000019073486</v>
+      </c>
+      <c r="I41" t="n">
+        <v>4.174757204245461</v>
+      </c>
+      <c r="J41" t="n">
+        <v>50</v>
+      </c>
+      <c r="K41" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>IGD SIIQ S.p.A.</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>IT0005322612</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>3.964999914169312</v>
+      </c>
+      <c r="I42" t="n">
+        <v>3.783102225651013</v>
+      </c>
+      <c r="J42" t="n">
+        <v>50</v>
+      </c>
+      <c r="K42" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>INTERCOS S.p.A.</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.197169</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>IT0005455875</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>11.47999954223633</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.717500068485116</v>
+      </c>
+      <c r="J43" t="n">
+        <v>50</v>
+      </c>
+      <c r="K43" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ITALMOBILIARE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>IT0005253205</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="I44" t="n">
+        <v>4.356435643564357</v>
+      </c>
+      <c r="J44" t="n">
+        <v>50</v>
+      </c>
+      <c r="K44" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>VALSOIA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>IT0001018362</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="I45" t="n">
+        <v>3.707317073170731</v>
+      </c>
+      <c r="J45" t="n">
+        <v>50</v>
+      </c>
+      <c r="K45" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>WIIT S.p.A.</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>IT0005440893</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>28</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1.071428571428571</v>
+      </c>
+      <c r="J46" t="n">
+        <v>50</v>
+      </c>
+      <c r="K46" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Basic Net S.p.A.</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>IT0001033700</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>5.78000020980835</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2.768165989483679</v>
+      </c>
+      <c r="J47" t="n">
+        <v>43</v>
+      </c>
+      <c r="K47" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>EDISON S.p.A.</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>IT0003372205</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>2.210000038146973</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2.941176419820373</v>
+      </c>
+      <c r="J48" t="n">
+        <v>43</v>
+      </c>
+      <c r="K48" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Fiera Milano S.p.A</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>IT0003365613</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>7.159999847412109</v>
+      </c>
+      <c r="I49" t="n">
+        <v>3.491620186142313</v>
+      </c>
+      <c r="J49" t="n">
+        <v>43</v>
+      </c>
+      <c r="K49" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Anima Holding S.p.A.</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>IT0004998065</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>6.614999771118164</v>
+      </c>
+      <c r="I50" t="n">
+        <v>7.558579248680498</v>
+      </c>
+      <c r="J50" t="n">
+        <v>36</v>
+      </c>
+      <c r="K50" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Banco BPM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>IT0005218380</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>11.43000030517578</v>
+      </c>
+      <c r="I51" t="n">
+        <v>4.724409322679326</v>
+      </c>
+      <c r="J51" t="n">
+        <v>36</v>
+      </c>
+      <c r="K51" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Davide Campari-Milano N.V.</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>NL0015435975</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>6.176000118255615</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1.619170953452711</v>
+      </c>
+      <c r="J52" t="n">
+        <v>36</v>
+      </c>
+      <c r="K52" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>IT0005215329</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>9.100000381469727</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1.758241684536706</v>
+      </c>
+      <c r="J53" t="n">
+        <v>36</v>
+      </c>
+      <c r="K53" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Ferrari N.V.</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>3.615</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>NL0011585146</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>289.2000122070312</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1.249999947237938</v>
+      </c>
+      <c r="J54" t="n">
+        <v>36</v>
+      </c>
+      <c r="K54" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Generalfinance S.p.A.</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>IT0005144784</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>26.39999961853027</v>
+      </c>
+      <c r="I55" t="n">
+        <v>5.151515225952543</v>
+      </c>
+      <c r="J55" t="n">
+        <v>36</v>
+      </c>
+      <c r="K55" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>MAIRE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>IT0004931058</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>12.86999988555908</v>
+      </c>
+      <c r="I56" t="n">
+        <v>4.545454585873038</v>
+      </c>
+      <c r="J56" t="n">
+        <v>36</v>
+      </c>
+      <c r="K56" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>IT0000062957</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>15.77000045776367</v>
+      </c>
+      <c r="I57" t="n">
+        <v>3.994926960765223</v>
+      </c>
+      <c r="J57" t="n">
+        <v>36</v>
+      </c>
+      <c r="K57" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Prysmian S.p.A.</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>IT0004176001</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>98.41999816894531</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.914448299882187</v>
+      </c>
+      <c r="J58" t="n">
+        <v>36</v>
+      </c>
+      <c r="K58" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unicredit S.p.A.</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1.7208</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>IT0005239360</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="I59" t="n">
+        <v>2.70992125984252</v>
+      </c>
+      <c r="J59" t="n">
+        <v>36</v>
+      </c>
+      <c r="K59" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>IT0001214433</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>22.20000076293945</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.6306306089579743</v>
+      </c>
+      <c r="J60" t="n">
+        <v>29</v>
+      </c>
+      <c r="K60" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Reti S.p.A.</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>IT0005418204</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>1.509999990463257</v>
+      </c>
+      <c r="I61" t="n">
+        <v>3.973509958870426</v>
+      </c>
+      <c r="J61" t="n">
+        <v>29</v>
+      </c>
+      <c r="K61" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Confinvest F.L. S.p.A.</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>IT0005379604</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>1.929999947547913</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1.7616580789651</v>
+      </c>
+      <c r="J62" t="n">
+        <v>15</v>
+      </c>
+      <c r="K62" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Eni S.p.A.</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Interim</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>IT0003132476</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>22.35000038146973</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1.163310942113293</v>
+      </c>
+      <c r="J63" t="n">
+        <v>8</v>
+      </c>
+      <c r="K63" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>STMicroelectronics N.V.</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B64" t="n">
         <v>0.09</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>DOLLARI USA</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Interim</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>NL0000226223</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="H64" t="n">
         <v>28.61499977111816</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I64" t="n">
         <v>0.3145203589721474</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J64" t="n">
         <v>8</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K64" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Banca Generali S.p.A.</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Interim</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>IT0001031084</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>50.29999923706055</v>
+      </c>
+      <c r="I65" t="n">
+        <v>1.292246540475266</v>
+      </c>
+      <c r="J65" t="n">
+        <v>-20</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-18</v>
       </c>
     </row>
   </sheetData>
@@ -969,7 +3507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C313"/>
+  <dimension ref="A1:C303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2148,7 +4686,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2165,7 +4703,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2182,7 +4720,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2199,7 +4737,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2216,7 +4754,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2233,7 +4771,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2243,7 +4781,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2301,7 +4839,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2328,14 +4866,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2352,7 +4890,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2369,7 +4907,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2379,14 +4917,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2403,7 +4941,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2413,14 +4951,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2430,14 +4968,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>Antares Vision S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2454,7 +4992,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2471,7 +5009,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2488,7 +5026,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2505,7 +5043,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Antares Vision S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2522,7 +5060,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2539,7 +5077,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2549,14 +5087,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2573,7 +5111,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2590,7 +5128,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2607,7 +5145,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2617,14 +5155,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2634,14 +5172,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2651,14 +5189,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2668,14 +5206,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2692,7 +5230,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2702,7 +5240,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -2726,7 +5264,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2743,7 +5281,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2753,14 +5291,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2770,14 +5308,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2794,7 +5332,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2811,7 +5349,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2828,7 +5366,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2845,7 +5383,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2855,7 +5393,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2879,7 +5417,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2896,7 +5434,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2913,7 +5451,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2923,14 +5461,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2940,14 +5478,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2964,7 +5502,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2981,7 +5519,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3015,7 +5553,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3032,7 +5570,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3049,7 +5587,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3059,14 +5597,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3076,14 +5614,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3093,14 +5631,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3117,7 +5655,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3134,7 +5672,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3151,7 +5689,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3161,14 +5699,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3185,7 +5723,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3195,14 +5733,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3219,7 +5757,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3236,7 +5774,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3246,14 +5784,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3270,7 +5808,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3280,14 +5818,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3304,7 +5842,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3314,7 +5852,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3338,7 +5876,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3348,14 +5886,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3372,7 +5910,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3382,14 +5920,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3406,7 +5944,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3423,7 +5961,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3433,14 +5971,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3457,7 +5995,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3474,7 +6012,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3491,7 +6029,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3501,14 +6039,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3518,14 +6056,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3542,7 +6080,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3552,14 +6090,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3576,7 +6114,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3586,14 +6124,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3610,7 +6148,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -3627,7 +6165,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -3637,14 +6175,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -3654,14 +6192,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -3678,7 +6216,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -3688,14 +6226,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -3712,7 +6250,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -3729,7 +6267,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -3746,7 +6284,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -3763,7 +6301,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -3773,14 +6311,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -3797,7 +6335,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -3814,7 +6352,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3831,7 +6369,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -3848,7 +6386,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -3882,7 +6420,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -3892,14 +6430,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -3916,7 +6454,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -3933,7 +6471,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -3950,7 +6488,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -3960,14 +6498,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -3984,7 +6522,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4001,7 +6539,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4018,7 +6556,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4035,7 +6573,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4045,14 +6583,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4069,7 +6607,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4086,7 +6624,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ELES S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4103,7 +6641,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4120,7 +6658,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4137,7 +6675,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4154,7 +6692,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4171,7 +6709,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4188,7 +6726,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4205,7 +6743,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4222,7 +6760,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4239,7 +6777,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4256,7 +6794,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4290,7 +6828,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4307,7 +6845,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4324,7 +6862,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4341,7 +6879,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>ELES S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4358,7 +6896,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4375,7 +6913,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4392,7 +6930,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4409,7 +6947,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4419,14 +6957,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4443,7 +6981,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4460,7 +6998,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -4477,7 +7015,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>HEALTH ITALIA S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -4494,7 +7032,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -4511,7 +7049,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -4528,7 +7066,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -4545,7 +7083,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -4562,7 +7100,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -4579,7 +7117,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -4589,14 +7127,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -4613,7 +7151,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -4630,7 +7168,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -4640,14 +7178,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -4664,7 +7202,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -4681,7 +7219,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -4691,14 +7229,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -4715,7 +7253,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -4732,7 +7270,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -4749,7 +7287,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -4759,14 +7297,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -4783,7 +7321,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -4800,7 +7338,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -4817,7 +7355,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -4834,7 +7372,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -4851,7 +7389,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -4868,7 +7406,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -4885,7 +7423,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -4902,7 +7440,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -4912,14 +7450,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -4936,7 +7474,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -4953,7 +7491,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -4970,7 +7508,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -4987,7 +7525,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5004,7 +7542,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5021,7 +7559,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5038,7 +7576,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5055,7 +7593,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5065,14 +7603,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5089,12 +7627,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -5106,29 +7644,29 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -5140,12 +7678,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -5157,12 +7695,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -5174,12 +7712,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -5191,29 +7729,29 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -5225,12 +7763,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -5242,12 +7780,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -5259,7 +7797,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -5269,14 +7807,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5286,14 +7824,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -5310,7 +7848,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -5320,7 +7858,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -5344,7 +7882,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -5354,14 +7892,14 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -5378,7 +7916,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -5388,14 +7926,14 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -5412,7 +7950,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -5422,14 +7960,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -5446,7 +7984,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -5463,7 +8001,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -5480,7 +8018,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -5490,14 +8028,14 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -5514,7 +8052,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -5531,7 +8069,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -5548,7 +8086,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -5565,7 +8103,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -5582,7 +8120,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -5599,7 +8137,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -5616,7 +8154,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -5633,7 +8171,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -5650,7 +8188,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -5667,7 +8205,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -5684,7 +8222,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -5701,7 +8239,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -5711,36 +8249,36 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -5752,29 +8290,29 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -5786,46 +8324,46 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -5837,80 +8375,80 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -5922,46 +8460,46 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
+          <t>RT&amp;L S.P.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -5973,321 +8511,151 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>Generalfinance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>RT&amp;L S.P.A.</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>Masi Agricola S.p.A.</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>Growens S.p.A.</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>Triboo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
-        </is>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>Vimi Fasteners S.p.A.</t>
-        </is>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>BASTOGI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>Stellantis N.V.</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
         <is>
           <t>Annual General Meeting</t>
         </is>
@@ -6317,112 +8685,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BASTOGI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Stellantis N.V.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Triboo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Vimi Fasteners S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>